--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-04-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-04-2025.xlsx
@@ -134,6 +134,176 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.40</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>£12.29</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.51</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.95</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>£16.25</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>£18.48</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>£17.82</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>£18.58</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>£21.88</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>£23.63</t>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>£24.10</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>£26.79</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>£25.05</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>£25.83</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
+      <text>
+        <t>£28.88</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>£29.68</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
+      <text>
+        <t>£30.00</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>£31.89</t>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0">
+      <text>
+        <t>£29.38</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>£31.86</t>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0">
+      <text>
+        <t>£36.88</t>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <t>£38.00</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>£38.48</t>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0">
+      <text>
+        <t>£43.99</t>
+      </text>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0">
+      <text>
+        <t>£46.73</t>
+      </text>
+    </comment>
+    <comment ref="I15" authorId="0" shapeId="0">
+      <text>
+        <t>£44.94</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>£47.28</t>
+      </text>
+    </comment>
+    <comment ref="I16" authorId="0" shapeId="0">
+      <text>
+        <t>£45.38</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>£49.48</t>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0" shapeId="0">
+      <text>
+        <t>£518.2</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>£513.3</t>
+      </text>
+    </comment>
+    <comment ref="L25" authorId="0" shapeId="0">
+      <text>
+        <t>£520.12</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2855,5 +3025,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>